--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_F_day_ahead_forecast_sample.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_F_day_ahead_forecast_sample.xlsx
@@ -592,34 +592,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30.61588891969786</v>
+        <v>30.92321839471665</v>
       </c>
       <c r="D2" t="n">
-        <v>29.55491108046512</v>
+        <v>29.8515902110437</v>
       </c>
       <c r="E2" t="n">
-        <v>40.25770497900302</v>
+        <v>40.24027645506479</v>
       </c>
       <c r="F2" t="n">
-        <v>38.64749150268041</v>
+        <v>38.63076007869193</v>
       </c>
       <c r="G2" t="n">
-        <v>51.06267151813029</v>
+        <v>51.04056526559137</v>
       </c>
       <c r="H2" t="n">
-        <v>47.51784632108186</v>
+        <v>47.51784632107597</v>
       </c>
       <c r="I2" t="n">
-        <v>45.07584900922934</v>
+        <v>45.07584900922375</v>
       </c>
       <c r="J2" t="n">
-        <v>48.06720466968298</v>
+        <v>48.06720466967701</v>
       </c>
       <c r="K2" t="n">
-        <v>21.52757905780578</v>
+        <v>21.45359415377609</v>
       </c>
       <c r="L2" t="n">
-        <v>21.33646594216627</v>
+        <v>21.26313784610748</v>
       </c>
       <c r="M2" t="n">
         <v>34.5</v>
@@ -628,40 +628,40 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>47.11138718791239</v>
+        <v>47.1188927421153</v>
       </c>
       <c r="P2" t="n">
-        <v>28.13990644456792</v>
+        <v>28.1443895558854</v>
       </c>
       <c r="Q2" t="n">
-        <v>47.77535636747315</v>
+        <v>47.78296770197598</v>
       </c>
       <c r="R2" t="n">
-        <v>22.25289744149498</v>
+        <v>22.1698603010651</v>
       </c>
       <c r="S2" t="n">
-        <v>21.9918025584864</v>
+        <v>21.90973969893491</v>
       </c>
       <c r="T2" t="n">
-        <v>60.17080000016298</v>
+        <v>60.77480860576034</v>
       </c>
       <c r="U2" t="n">
-        <v>129.9678679998137</v>
+        <v>129.9116017993481</v>
       </c>
       <c r="V2" t="n">
-        <v>140.6608999999942</v>
+        <v>140.6608999999767</v>
       </c>
       <c r="W2" t="n">
-        <v>42.86404499997206</v>
+        <v>42.71673199988358</v>
       </c>
       <c r="X2" t="n">
-        <v>157.5266499999535</v>
+        <v>157.5462499999767</v>
       </c>
       <c r="Y2" t="n">
-        <v>44.24469999998138</v>
+        <v>44.0796</v>
       </c>
       <c r="Z2" t="n">
-        <v>575.4349629998778</v>
+        <v>575.6898924049455</v>
       </c>
     </row>
     <row r="3">
@@ -674,34 +674,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.55570512176504</v>
+        <v>30.85422728469485</v>
       </c>
       <c r="D3" t="n">
-        <v>29.61469087856092</v>
+        <v>29.90401955025531</v>
       </c>
       <c r="E3" t="n">
-        <v>40.33009320571262</v>
+        <v>40.30785387394292</v>
       </c>
       <c r="F3" t="n">
-        <v>38.12425614044604</v>
+        <v>38.10323317934215</v>
       </c>
       <c r="G3" t="n">
-        <v>51.50978665346879</v>
+        <v>51.48138247327189</v>
       </c>
       <c r="H3" t="n">
-        <v>47.4091831941534</v>
+        <v>47.4090146732157</v>
       </c>
       <c r="I3" t="n">
-        <v>45.15990475554955</v>
+        <v>45.15974422990909</v>
       </c>
       <c r="J3" t="n">
-        <v>48.0935120502854</v>
+        <v>48.09334109682867</v>
       </c>
       <c r="K3" t="n">
-        <v>23.63555206778987</v>
+        <v>21.26581828423675</v>
       </c>
       <c r="L3" t="n">
-        <v>23.6087614321738</v>
+        <v>21.2417137155304</v>
       </c>
       <c r="M3" t="n">
         <v>34.5</v>
@@ -710,40 +710,40 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>45.80690522624645</v>
+        <v>45.87691140572726</v>
       </c>
       <c r="P3" t="n">
-        <v>27.21309477366047</v>
+        <v>27.25468859422616</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>22.41839901717974</v>
+        <v>21.9279010590183</v>
       </c>
       <c r="S3" t="n">
-        <v>22.09042098278674</v>
+        <v>21.6070989409817</v>
       </c>
       <c r="T3" t="n">
-        <v>60.17039600032597</v>
+        <v>60.75824683495016</v>
       </c>
       <c r="U3" t="n">
-        <v>129.9641359996274</v>
+        <v>129.892469526557</v>
       </c>
       <c r="V3" t="n">
-        <v>140.6625999999883</v>
+        <v>140.6620999999535</v>
       </c>
       <c r="W3" t="n">
-        <v>47.24431349996368</v>
+        <v>42.50753199976715</v>
       </c>
       <c r="X3" t="n">
-        <v>157.5199999999069</v>
+        <v>157.6315999999534</v>
       </c>
       <c r="Y3" t="n">
-        <v>44.50881999996648</v>
+        <v>43.535</v>
       </c>
       <c r="Z3" t="n">
-        <v>580.0702654997789</v>
+        <v>574.9869483611811</v>
       </c>
     </row>
     <row r="4">
@@ -756,34 +756,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.54244528977145</v>
+        <v>30.74290196385661</v>
       </c>
       <c r="D4" t="n">
-        <v>29.6275467107175</v>
+        <v>29.8219987075562</v>
       </c>
       <c r="E4" t="n">
-        <v>40.47056678104087</v>
+        <v>40.45011529670212</v>
       </c>
       <c r="F4" t="n">
-        <v>37.81669275041624</v>
+        <v>37.79758238055874</v>
       </c>
       <c r="G4" t="n">
-        <v>51.67314446798405</v>
+        <v>51.6470318486442</v>
       </c>
       <c r="H4" t="n">
-        <v>47.35410925460804</v>
+        <v>47.35350329133848</v>
       </c>
       <c r="I4" t="n">
-        <v>45.20301653325497</v>
+        <v>45.20243809628037</v>
       </c>
       <c r="J4" t="n">
-        <v>48.10717421211951</v>
+        <v>48.10655861231131</v>
       </c>
       <c r="K4" t="n">
-        <v>23.9706500908276</v>
+        <v>21.18067693829964</v>
       </c>
       <c r="L4" t="n">
-        <v>24.04067895913358</v>
+        <v>21.24255506135109</v>
       </c>
       <c r="M4" t="n">
         <v>34.5</v>
@@ -792,40 +792,40 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>46.89776438799272</v>
+        <v>46.89262748528097</v>
       </c>
       <c r="P4" t="n">
-        <v>26.11558561186767</v>
+        <v>26.11392251464918</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
       </c>
       <c r="R4" t="n">
-        <v>22.6275121602193</v>
+        <v>21.67437488962295</v>
       </c>
       <c r="S4" t="n">
-        <v>22.25340383973526</v>
+        <v>21.31602511037705</v>
       </c>
       <c r="T4" t="n">
-        <v>60.16999200048895</v>
+        <v>60.5649006714128</v>
       </c>
       <c r="U4" t="n">
-        <v>129.9604039994412</v>
+        <v>129.8947295259051</v>
       </c>
       <c r="V4" t="n">
-        <v>140.6642999999825</v>
+        <v>140.6624999999302</v>
       </c>
       <c r="W4" t="n">
-        <v>48.01132904996118</v>
+        <v>42.42323199965074</v>
       </c>
       <c r="X4" t="n">
-        <v>157.5133499998604</v>
+        <v>157.5065499999301</v>
       </c>
       <c r="Y4" t="n">
-        <v>44.88091599995456</v>
+        <v>42.99039999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>581.2002910496888</v>
+        <v>574.0423121968289</v>
       </c>
     </row>
     <row r="5">
@@ -838,34 +838,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.53265654430785</v>
+        <v>30.60427309394151</v>
       </c>
       <c r="D5" t="n">
-        <v>29.63693145634408</v>
+        <v>29.70644701813454</v>
       </c>
       <c r="E5" t="n">
-        <v>40.53501259296716</v>
+        <v>40.49779607120789</v>
       </c>
       <c r="F5" t="n">
-        <v>37.68477077546862</v>
+        <v>37.65017115400948</v>
       </c>
       <c r="G5" t="n">
-        <v>51.7368886308191</v>
+        <v>51.68938730003577</v>
       </c>
       <c r="H5" t="n">
-        <v>47.32592717828864</v>
+        <v>47.32024131125171</v>
       </c>
       <c r="I5" t="n">
-        <v>45.22419529535298</v>
+        <v>45.2187619361642</v>
       </c>
       <c r="J5" t="n">
-        <v>48.11587752633508</v>
+        <v>48.11009675249098</v>
       </c>
       <c r="K5" t="n">
-        <v>23.41020156494927</v>
+        <v>20.92105843855658</v>
       </c>
       <c r="L5" t="n">
-        <v>23.52334715001114</v>
+        <v>21.02217356097774</v>
       </c>
       <c r="M5" t="n">
         <v>34.5</v>
@@ -874,40 +874,40 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47.37011316330859</v>
+        <v>47.33931310078938</v>
       </c>
       <c r="P5" t="n">
-        <v>25.63658683650529</v>
+        <v>25.62088689911743</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>22.80189056068129</v>
+        <v>21.40273770054917</v>
       </c>
       <c r="S5" t="n">
-        <v>22.41870223926373</v>
+        <v>21.04306229945082</v>
       </c>
       <c r="T5" t="n">
-        <v>60.16958800065193</v>
+        <v>60.31072011207604</v>
       </c>
       <c r="U5" t="n">
-        <v>129.9566719992549</v>
+        <v>129.8373545252531</v>
       </c>
       <c r="V5" t="n">
-        <v>140.6659999999767</v>
+        <v>140.6490999999069</v>
       </c>
       <c r="W5" t="n">
-        <v>46.93354871496041</v>
+        <v>41.94323199953432</v>
       </c>
       <c r="X5" t="n">
-        <v>157.5066999998139</v>
+        <v>157.4601999999068</v>
       </c>
       <c r="Y5" t="n">
-        <v>45.22059279994502</v>
+        <v>42.44579999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>580.4531015146028</v>
+        <v>572.6464066366772</v>
       </c>
     </row>
     <row r="6">
@@ -920,34 +920,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30.54446002713636</v>
+        <v>30.61258772299257</v>
       </c>
       <c r="D6" t="n">
-        <v>29.62472397367855</v>
+        <v>29.69080025012638</v>
       </c>
       <c r="E6" t="n">
-        <v>40.5714395585258</v>
+        <v>40.51008878925865</v>
       </c>
       <c r="F6" t="n">
-        <v>37.60228367226961</v>
+        <v>37.5454227608847</v>
       </c>
       <c r="G6" t="n">
-        <v>51.77921676827317</v>
+        <v>51.70091797445784</v>
       </c>
       <c r="H6" t="n">
-        <v>47.31401285417432</v>
+        <v>47.31418103068035</v>
       </c>
       <c r="I6" t="n">
-        <v>45.23633838040283</v>
+        <v>45.23649917186556</v>
       </c>
       <c r="J6" t="n">
-        <v>48.11734876539374</v>
+        <v>48.1175197973377</v>
       </c>
       <c r="K6" t="n">
-        <v>23.96559330966973</v>
+        <v>21.07332407541546</v>
       </c>
       <c r="L6" t="n">
-        <v>24.10955130479045</v>
+        <v>21.19990861038718</v>
       </c>
       <c r="M6" t="n">
         <v>34.5</v>
@@ -956,40 +956,40 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>48.09272070479457</v>
+        <v>48.02556588387367</v>
       </c>
       <c r="P6" t="n">
-        <v>24.90732929497277</v>
+        <v>24.87303411600983</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>22.7322677706289</v>
+        <v>21.13384145854958</v>
       </c>
       <c r="S6" t="n">
-        <v>22.33806646930849</v>
+        <v>20.76735854145041</v>
       </c>
       <c r="T6" t="n">
-        <v>60.16918400081491</v>
+        <v>60.30338797311896</v>
       </c>
       <c r="U6" t="n">
-        <v>129.9529399990686</v>
+        <v>129.7564295246012</v>
       </c>
       <c r="V6" t="n">
-        <v>140.6676999999709</v>
+        <v>140.6681999998836</v>
       </c>
       <c r="W6" t="n">
-        <v>48.07514461446019</v>
+        <v>42.27323268580264</v>
       </c>
       <c r="X6" t="n">
-        <v>157.5000499997673</v>
+        <v>157.3985999998835</v>
       </c>
       <c r="Y6" t="n">
-        <v>45.0703342399374</v>
+        <v>41.90119999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>581.4353528540194</v>
+        <v>572.3010501832899</v>
       </c>
     </row>
     <row r="7">
@@ -1002,34 +1002,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.51344313810524</v>
+        <v>30.7115309376579</v>
       </c>
       <c r="D7" t="n">
-        <v>29.65533686287265</v>
+        <v>29.84785399040794</v>
       </c>
       <c r="E7" t="n">
-        <v>40.47602502964533</v>
+        <v>40.39962673646984</v>
       </c>
       <c r="F7" t="n">
-        <v>37.61731247721042</v>
+        <v>37.54630998956488</v>
       </c>
       <c r="G7" t="n">
-        <v>51.85587049202653</v>
+        <v>51.75799279791455</v>
       </c>
       <c r="H7" t="n">
-        <v>47.3049613930439</v>
+        <v>47.31239328400122</v>
       </c>
       <c r="I7" t="n">
-        <v>45.24351082382571</v>
+        <v>45.25061884863047</v>
       </c>
       <c r="J7" t="n">
-        <v>48.12092778309543</v>
+        <v>48.12848786722865</v>
       </c>
       <c r="K7" t="n">
-        <v>23.81241294942705</v>
+        <v>20.92047478568053</v>
       </c>
       <c r="L7" t="n">
-        <v>23.95638043488307</v>
+        <v>21.04695790000569</v>
       </c>
       <c r="M7" t="n">
         <v>34.5</v>
@@ -1038,40 +1038,40 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>48.69898713124955</v>
+        <v>48.56449988217273</v>
       </c>
       <c r="P7" t="n">
-        <v>24.29441286847126</v>
+        <v>24.22715011768749</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>21.76304572491652</v>
+        <v>20.86017027135711</v>
       </c>
       <c r="S7" t="n">
-        <v>21.38356166701477</v>
+        <v>20.49642972864287</v>
       </c>
       <c r="T7" t="n">
-        <v>60.16878000097789</v>
+        <v>60.55938492806584</v>
       </c>
       <c r="U7" t="n">
-        <v>129.9492079988823</v>
+        <v>129.7039295239493</v>
       </c>
       <c r="V7" t="n">
-        <v>140.669399999965</v>
+        <v>140.6914999998603</v>
       </c>
       <c r="W7" t="n">
-        <v>47.76879338431011</v>
+        <v>41.96743268568622</v>
       </c>
       <c r="X7" t="n">
-        <v>157.4933999997208</v>
+        <v>157.2916499998602</v>
       </c>
       <c r="Y7" t="n">
-        <v>43.14660739193129</v>
+        <v>41.35659999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>579.1961887757874</v>
+        <v>571.5704971374219</v>
       </c>
     </row>
     <row r="8">
@@ -1084,34 +1084,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.51336369279125</v>
+        <v>30.29624139231642</v>
       </c>
       <c r="D8" t="n">
-        <v>29.65501230834962</v>
+        <v>29.44399773264358</v>
       </c>
       <c r="E8" t="n">
-        <v>40.3843051014321</v>
+        <v>40.29059139513013</v>
       </c>
       <c r="F8" t="n">
-        <v>37.62794183819235</v>
+        <v>37.54062440432008</v>
       </c>
       <c r="G8" t="n">
-        <v>51.93322905907154</v>
+        <v>51.81271552384714</v>
       </c>
       <c r="H8" t="n">
-        <v>47.29788033293057</v>
+        <v>47.30149480816964</v>
       </c>
       <c r="I8" t="n">
-        <v>45.24859896871777</v>
+        <v>45.25205683912178</v>
       </c>
       <c r="J8" t="n">
-        <v>48.12462069831086</v>
+        <v>48.12829835254567</v>
       </c>
       <c r="K8" t="n">
-        <v>23.48330999808825</v>
+        <v>20.68388857734242</v>
       </c>
       <c r="L8" t="n">
-        <v>23.55773801717685</v>
+        <v>20.74944410822738</v>
       </c>
       <c r="M8" t="n">
         <v>34.5</v>
@@ -1120,40 +1120,40 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>49.23629235917743</v>
+        <v>49.0741087479317</v>
       </c>
       <c r="P8" t="n">
-        <v>23.75045764049682</v>
+        <v>23.6710912519052</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>21.38549954640445</v>
+        <v>20.58861835750839</v>
       </c>
       <c r="S8" t="n">
-        <v>21.00612636712195</v>
+        <v>20.2233816424916</v>
       </c>
       <c r="T8" t="n">
-        <v>60.16837600114087</v>
+        <v>59.74023912496001</v>
       </c>
       <c r="U8" t="n">
-        <v>129.945475998696</v>
+        <v>129.6439313232974</v>
       </c>
       <c r="V8" t="n">
-        <v>140.6710999999592</v>
+        <v>140.6818499998371</v>
       </c>
       <c r="W8" t="n">
-        <v>47.04104801526509</v>
+        <v>41.43333268556979</v>
       </c>
       <c r="X8" t="n">
-        <v>157.4867499996743</v>
+        <v>157.2451999998369</v>
       </c>
       <c r="Y8" t="n">
-        <v>42.39162591352641</v>
+        <v>40.81199999999998</v>
       </c>
       <c r="Z8" t="n">
-        <v>577.7043759282619</v>
+        <v>569.5565531335011</v>
       </c>
     </row>
     <row r="9">
@@ -1166,34 +1166,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.51534116562963</v>
+        <v>30.16575912750297</v>
       </c>
       <c r="D9" t="n">
-        <v>29.65263083567422</v>
+        <v>29.31293195873596</v>
       </c>
       <c r="E9" t="n">
-        <v>40.3189876405435</v>
+        <v>40.19898559744826</v>
       </c>
       <c r="F9" t="n">
-        <v>37.64778998630524</v>
+        <v>37.5357382712013</v>
       </c>
       <c r="G9" t="n">
-        <v>51.97496637166095</v>
+        <v>51.82027245399586</v>
       </c>
       <c r="H9" t="n">
-        <v>47.29343164067087</v>
+        <v>47.27225138265394</v>
       </c>
       <c r="I9" t="n">
-        <v>45.25256979556851</v>
+        <v>45.23230353298302</v>
       </c>
       <c r="J9" t="n">
-        <v>48.126798563714</v>
+        <v>48.10524508417686</v>
       </c>
       <c r="K9" t="n">
-        <v>21.11768878097096</v>
+        <v>20.78393803409048</v>
       </c>
       <c r="L9" t="n">
-        <v>21.16296062358062</v>
+        <v>20.82849438593596</v>
       </c>
       <c r="M9" t="n">
         <v>34.5</v>
@@ -1205,37 +1205,37 @@
         <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>23.64095886724517</v>
+        <v>23.45965532860437</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.33914113238256</v>
+        <v>49.09969467120928</v>
       </c>
       <c r="R9" t="n">
-        <v>21.66396370576457</v>
+        <v>20.44043519153751</v>
       </c>
       <c r="S9" t="n">
-        <v>21.30565702392035</v>
+        <v>20.10236480846247</v>
       </c>
       <c r="T9" t="n">
-        <v>60.16797200130385</v>
+        <v>59.47869108623893</v>
       </c>
       <c r="U9" t="n">
-        <v>129.9417439985097</v>
+        <v>129.5549963226454</v>
       </c>
       <c r="V9" t="n">
-        <v>140.6727999999534</v>
+        <v>140.6097999998138</v>
       </c>
       <c r="W9" t="n">
-        <v>42.28064940455158</v>
+        <v>41.61243242002644</v>
       </c>
       <c r="X9" t="n">
-        <v>157.4800999996277</v>
+        <v>157.0593499998137</v>
       </c>
       <c r="Y9" t="n">
-        <v>42.96962072968491</v>
+        <v>40.54279999999998</v>
       </c>
       <c r="Z9" t="n">
-        <v>573.5128861336311</v>
+        <v>568.8580698285382</v>
       </c>
     </row>
     <row r="10">
@@ -1248,34 +1248,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30.50299450802217</v>
+        <v>30.71625697987322</v>
       </c>
       <c r="D10" t="n">
-        <v>29.66457349344466</v>
+        <v>29.87197412317482</v>
       </c>
       <c r="E10" t="n">
-        <v>40.30048876873748</v>
+        <v>40.16544387845632</v>
       </c>
       <c r="F10" t="n">
-        <v>37.63174890578039</v>
+        <v>37.50564682718695</v>
       </c>
       <c r="G10" t="n">
-        <v>52.00577432380554</v>
+        <v>51.83150561635023</v>
       </c>
       <c r="H10" t="n">
-        <v>47.2994361034174</v>
+        <v>47.29097983859735</v>
       </c>
       <c r="I10" t="n">
-        <v>45.24660033155245</v>
+        <v>45.23851107582066</v>
       </c>
       <c r="J10" t="n">
-        <v>48.1284635649777</v>
+        <v>48.11985908537255</v>
       </c>
       <c r="K10" t="n">
-        <v>20.58371748523562</v>
+        <v>20.91480508039769</v>
       </c>
       <c r="L10" t="n">
-        <v>20.56021773610191</v>
+        <v>20.89092733951233</v>
       </c>
       <c r="M10" t="n">
         <v>34.5</v>
@@ -1284,40 +1284,40 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>48.03584224172003</v>
+        <v>47.99627582554882</v>
       </c>
       <c r="P10" t="n">
-        <v>24.93760775786117</v>
+        <v>24.75387417424158</v>
       </c>
       <c r="Q10" t="n">
         <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>21.9710727954686</v>
+        <v>20.36433226682578</v>
       </c>
       <c r="S10" t="n">
-        <v>21.4801037882607</v>
+        <v>19.90926773317419</v>
       </c>
       <c r="T10" t="n">
-        <v>60.16756800146683</v>
+        <v>60.58823110304804</v>
       </c>
       <c r="U10" t="n">
-        <v>129.9380119983234</v>
+        <v>129.5025963219935</v>
       </c>
       <c r="V10" t="n">
-        <v>140.6744999999476</v>
+        <v>140.6493499997906</v>
       </c>
       <c r="W10" t="n">
-        <v>41.14393522133753</v>
+        <v>41.80573241991003</v>
       </c>
       <c r="X10" t="n">
-        <v>157.4734499995812</v>
+        <v>157.2501499997904</v>
       </c>
       <c r="Y10" t="n">
-        <v>43.45117658372931</v>
+        <v>40.27359999999997</v>
       </c>
       <c r="Z10" t="n">
-        <v>572.8486418043859</v>
+        <v>570.0696598445326</v>
       </c>
     </row>
     <row r="11">
@@ -1330,34 +1330,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30.48915104191385</v>
+        <v>30.3860000525997</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67801295971596</v>
+        <v>29.57760621524924</v>
       </c>
       <c r="E11" t="n">
-        <v>40.29476890602245</v>
+        <v>40.11924025545689</v>
       </c>
       <c r="F11" t="n">
-        <v>37.6168278777963</v>
+        <v>37.45296464653306</v>
       </c>
       <c r="G11" t="n">
-        <v>52.02268321431838</v>
+        <v>51.79606641935163</v>
       </c>
       <c r="H11" t="n">
-        <v>47.30778742630047</v>
+        <v>47.27674799825434</v>
       </c>
       <c r="I11" t="n">
-        <v>45.2420060657176</v>
+        <v>45.21232203126288</v>
       </c>
       <c r="J11" t="n">
-        <v>48.12640650792365</v>
+        <v>48.09482997025005</v>
       </c>
       <c r="K11" t="n">
-        <v>20.58945302905384</v>
+        <v>20.73042105002877</v>
       </c>
       <c r="L11" t="n">
-        <v>20.54137253731948</v>
+        <v>20.68201136976484</v>
       </c>
       <c r="M11" t="n">
         <v>34.5</v>
@@ -1366,40 +1366,40 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>48.03146478179255</v>
+        <v>47.89975567879422</v>
       </c>
       <c r="P11" t="n">
-        <v>24.93533521774211</v>
+        <v>24.70409432097282</v>
       </c>
       <c r="Q11" t="n">
         <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>22.06349802380385</v>
+        <v>20.22816521577603</v>
       </c>
       <c r="S11" t="n">
-        <v>21.57056324316096</v>
+        <v>19.77623478422393</v>
       </c>
       <c r="T11" t="n">
-        <v>60.16716400162981</v>
+        <v>59.96360626784893</v>
       </c>
       <c r="U11" t="n">
-        <v>129.9342799981372</v>
+        <v>129.3682713213416</v>
       </c>
       <c r="V11" t="n">
-        <v>140.6761999999417</v>
+        <v>140.5838999997673</v>
       </c>
       <c r="W11" t="n">
-        <v>41.13082556637332</v>
+        <v>41.41243241979362</v>
       </c>
       <c r="X11" t="n">
-        <v>157.4667999995347</v>
+        <v>157.103849999767</v>
       </c>
       <c r="Y11" t="n">
-        <v>43.63406126696481</v>
+        <v>40.00439999999996</v>
       </c>
       <c r="Z11" t="n">
-        <v>573.0093308325816</v>
+        <v>568.4364600085183</v>
       </c>
     </row>
     <row r="12">
@@ -1412,34 +1412,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.484830415767</v>
+        <v>30.15771537713173</v>
       </c>
       <c r="D12" t="n">
-        <v>29.6819295860258</v>
+        <v>29.36343001063435</v>
       </c>
       <c r="E12" t="n">
-        <v>40.29321096080481</v>
+        <v>40.10023514956224</v>
       </c>
       <c r="F12" t="n">
-        <v>37.61375185018341</v>
+        <v>37.43360874160299</v>
       </c>
       <c r="G12" t="n">
-        <v>52.02358518696268</v>
+        <v>51.77442922952442</v>
       </c>
       <c r="H12" t="n">
-        <v>47.31222707341241</v>
+        <v>47.29060195525313</v>
       </c>
       <c r="I12" t="n">
-        <v>45.24296005531134</v>
+        <v>45.22228074221213</v>
       </c>
       <c r="J12" t="n">
-        <v>48.12271287121215</v>
+        <v>48.10071730227877</v>
       </c>
       <c r="K12" t="n">
-        <v>20.84917948059179</v>
+        <v>20.77022711262234</v>
       </c>
       <c r="L12" t="n">
-        <v>20.78012818929226</v>
+        <v>20.70143730705487</v>
       </c>
       <c r="M12" t="n">
         <v>34.5</v>
@@ -1448,40 +1448,40 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>48.02708732186508</v>
+        <v>47.8577301603422</v>
       </c>
       <c r="P12" t="n">
-        <v>24.93306267762305</v>
+        <v>24.68241983940159</v>
       </c>
       <c r="Q12" t="n">
         <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>22.15856810269279</v>
+        <v>20.15250313862612</v>
       </c>
       <c r="S12" t="n">
-        <v>21.53204091086042</v>
+        <v>19.58269686137384</v>
       </c>
       <c r="T12" t="n">
-        <v>60.1667600017928</v>
+        <v>59.52114538776608</v>
       </c>
       <c r="U12" t="n">
-        <v>129.9305479979509</v>
+        <v>129.3082731206896</v>
       </c>
       <c r="V12" t="n">
-        <v>140.6778999999359</v>
+        <v>140.6135999997441</v>
       </c>
       <c r="W12" t="n">
-        <v>41.62930766988406</v>
+        <v>41.4716644196772</v>
       </c>
       <c r="X12" t="n">
-        <v>157.4601499994881</v>
+        <v>157.0401499997438</v>
       </c>
       <c r="Y12" t="n">
-        <v>43.69060901355321</v>
+        <v>39.73519999999996</v>
       </c>
       <c r="Z12" t="n">
-        <v>573.5552746826049</v>
+        <v>567.6900329276208</v>
       </c>
     </row>
     <row r="13">
@@ -1494,34 +1494,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30.4711402380728</v>
+        <v>29.85687818547341</v>
       </c>
       <c r="D13" t="n">
-        <v>29.69521576388298</v>
+        <v>29.09659542854308</v>
       </c>
       <c r="E13" t="n">
-        <v>40.29676202538628</v>
+        <v>40.0855290325577</v>
       </c>
       <c r="F13" t="n">
-        <v>37.61834286848518</v>
+        <v>37.42114997382144</v>
       </c>
       <c r="G13" t="n">
-        <v>52.01171110389315</v>
+        <v>51.73906911365857</v>
       </c>
       <c r="H13" t="n">
-        <v>47.31775562088163</v>
+        <v>47.29658231127427</v>
       </c>
       <c r="I13" t="n">
-        <v>45.24605831835753</v>
+        <v>45.22581203260884</v>
       </c>
       <c r="J13" t="n">
-        <v>48.11578606069093</v>
+        <v>48.09425565583769</v>
       </c>
       <c r="K13" t="n">
-        <v>19.08123020307502</v>
+        <v>20.87904276850983</v>
       </c>
       <c r="L13" t="n">
-        <v>19.01751249786227</v>
+        <v>20.80932165105097</v>
       </c>
       <c r="M13" t="n">
         <v>34.5</v>
@@ -1530,40 +1530,40 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>48.02270986193761</v>
+        <v>47.84895560153237</v>
       </c>
       <c r="P13" t="n">
-        <v>24.93079013750399</v>
+        <v>24.67789439818814</v>
       </c>
       <c r="Q13" t="n">
         <v>50</v>
       </c>
       <c r="R13" t="n">
-        <v>21.91853183673189</v>
+        <v>20.05673689658667</v>
       </c>
       <c r="S13" t="n">
-        <v>21.21095537390579</v>
+        <v>19.40926310341328</v>
       </c>
       <c r="T13" t="n">
-        <v>60.16635600195578</v>
+        <v>58.9534736140165</v>
       </c>
       <c r="U13" t="n">
-        <v>129.9268159977646</v>
+        <v>129.2457481200377</v>
       </c>
       <c r="V13" t="n">
-        <v>140.6795999999301</v>
+        <v>140.6166499997208</v>
       </c>
       <c r="W13" t="n">
-        <v>38.09874270093729</v>
+        <v>41.6883644195608</v>
       </c>
       <c r="X13" t="n">
-        <v>157.4534999994416</v>
+        <v>157.0268499997205</v>
       </c>
       <c r="Y13" t="n">
-        <v>43.12948721063768</v>
+        <v>39.46599999999995</v>
       </c>
       <c r="Z13" t="n">
-        <v>569.454501910667</v>
+        <v>566.9970861530562</v>
       </c>
     </row>
     <row r="14">
@@ -1576,34 +1576,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.47609160451681</v>
+        <v>30.12637155631195</v>
       </c>
       <c r="D14" t="n">
-        <v>29.68986039760194</v>
+        <v>29.34916253042838</v>
       </c>
       <c r="E14" t="n">
-        <v>40.30668678520849</v>
+        <v>40.07760279076206</v>
       </c>
       <c r="F14" t="n">
-        <v>37.60213290233096</v>
+        <v>37.38842030295818</v>
       </c>
       <c r="G14" t="n">
-        <v>52.01426431003887</v>
+        <v>51.71864002566556</v>
       </c>
       <c r="H14" t="n">
-        <v>47.3245310167862</v>
+        <v>47.32029243567029</v>
       </c>
       <c r="I14" t="n">
-        <v>45.24736544430183</v>
+        <v>45.24331290274259</v>
       </c>
       <c r="J14" t="n">
-        <v>48.1094035388362</v>
+        <v>48.10509466128462</v>
       </c>
       <c r="K14" t="n">
-        <v>19.62285328599329</v>
+        <v>20.87905082398997</v>
       </c>
       <c r="L14" t="n">
-        <v>19.55336452425995</v>
+        <v>20.8051135954544</v>
       </c>
       <c r="M14" t="n">
         <v>34.5</v>
@@ -1612,40 +1612,40 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>48.01833240201012</v>
+        <v>47.86300809041343</v>
       </c>
       <c r="P14" t="n">
-        <v>24.92851759738493</v>
+        <v>24.68514190928381</v>
       </c>
       <c r="Q14" t="n">
         <v>50</v>
       </c>
       <c r="R14" t="n">
-        <v>21.92737863747176</v>
+        <v>19.99807838041092</v>
       </c>
       <c r="S14" t="n">
-        <v>21.20123113101975</v>
+        <v>19.33582161958903</v>
       </c>
       <c r="T14" t="n">
-        <v>60.16595200211876</v>
+        <v>59.47553408674033</v>
       </c>
       <c r="U14" t="n">
-        <v>129.9230839975783</v>
+        <v>129.1846631193858</v>
       </c>
       <c r="V14" t="n">
-        <v>140.6812999999242</v>
+        <v>140.6686999996975</v>
       </c>
       <c r="W14" t="n">
-        <v>39.17621781025325</v>
+        <v>41.68416441944437</v>
       </c>
       <c r="X14" t="n">
-        <v>157.4468499993951</v>
+        <v>157.0481499996972</v>
       </c>
       <c r="Y14" t="n">
-        <v>43.12860976849151</v>
+        <v>39.33389999999996</v>
       </c>
       <c r="Z14" t="n">
-        <v>570.5220135777612</v>
+        <v>567.3951116249652</v>
       </c>
     </row>
     <row r="15">
@@ -1658,34 +1658,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30.47497757822825</v>
+        <v>30.33744974551506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.69057042405349</v>
+        <v>29.55658247305477</v>
       </c>
       <c r="E15" t="n">
-        <v>40.30598011500255</v>
+        <v>40.05019350348218</v>
       </c>
       <c r="F15" t="n">
-        <v>37.59512912541031</v>
+        <v>37.35654590125296</v>
       </c>
       <c r="G15" t="n">
-        <v>52.01824275697916</v>
+        <v>51.68812871399873</v>
       </c>
       <c r="H15" t="n">
-        <v>47.3205005801497</v>
+        <v>47.29902382763802</v>
       </c>
       <c r="I15" t="n">
-        <v>45.25186343411276</v>
+        <v>45.23132554757835</v>
       </c>
       <c r="J15" t="n">
-        <v>48.11063598565597</v>
+        <v>48.08880062445785</v>
       </c>
       <c r="K15" t="n">
-        <v>20.1774197435813</v>
+        <v>20.8734969344355</v>
       </c>
       <c r="L15" t="n">
-        <v>20.10943559946674</v>
+        <v>20.80316748489244</v>
       </c>
       <c r="M15" t="n">
         <v>34.5</v>
@@ -1694,40 +1694,40 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>48.01395494208266</v>
+        <v>47.78482875076311</v>
       </c>
       <c r="P15" t="n">
-        <v>24.92624505726587</v>
+        <v>24.64482124891084</v>
       </c>
       <c r="Q15" t="n">
         <v>50</v>
       </c>
       <c r="R15" t="n">
-        <v>21.74276031569448</v>
+        <v>19.95770321163675</v>
       </c>
       <c r="S15" t="n">
-        <v>20.9653274990801</v>
+        <v>19.24409678836321</v>
       </c>
       <c r="T15" t="n">
-        <v>60.16554800228174</v>
+        <v>59.89403221856983</v>
       </c>
       <c r="U15" t="n">
-        <v>129.919351997392</v>
+        <v>129.0948681187339</v>
       </c>
       <c r="V15" t="n">
-        <v>140.6829999999184</v>
+        <v>140.6191499996742</v>
       </c>
       <c r="W15" t="n">
-        <v>40.28685534304804</v>
+        <v>41.67666441932795</v>
       </c>
       <c r="X15" t="n">
-        <v>157.4401999993485</v>
+        <v>156.929649999674</v>
       </c>
       <c r="Y15" t="n">
-        <v>42.70808781477458</v>
+        <v>39.20179999999996</v>
       </c>
       <c r="Z15" t="n">
-        <v>571.2030431567633</v>
+        <v>567.4161647559798</v>
       </c>
     </row>
     <row r="16">
@@ -1740,34 +1740,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.47030585837742</v>
+        <v>30.09290224049235</v>
       </c>
       <c r="D16" t="n">
-        <v>29.6948381440673</v>
+        <v>29.32703942881412</v>
       </c>
       <c r="E16" t="n">
-        <v>40.30568240555133</v>
+        <v>40.02768515370514</v>
       </c>
       <c r="F16" t="n">
-        <v>37.58786799184541</v>
+        <v>37.32861611020375</v>
       </c>
       <c r="G16" t="n">
-        <v>52.02206959980901</v>
+        <v>51.66326182083176</v>
       </c>
       <c r="H16" t="n">
-        <v>47.31637310263805</v>
+        <v>47.28931541812445</v>
       </c>
       <c r="I16" t="n">
-        <v>45.25308605037144</v>
+        <v>45.22720824855933</v>
       </c>
       <c r="J16" t="n">
-        <v>48.11524084690311</v>
+        <v>48.08772633296715</v>
       </c>
       <c r="K16" t="n">
-        <v>20.59600449025791</v>
+        <v>20.92348838839091</v>
       </c>
       <c r="L16" t="n">
-        <v>20.52590671262856</v>
+        <v>20.85227603082062</v>
       </c>
       <c r="M16" t="n">
         <v>34.5</v>
@@ -1776,40 +1776,40 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>48.00957748215517</v>
+        <v>47.77687886853172</v>
       </c>
       <c r="P16" t="n">
-        <v>24.92397251714681</v>
+        <v>24.64072113111898</v>
       </c>
       <c r="Q16" t="n">
         <v>50</v>
       </c>
       <c r="R16" t="n">
-        <v>21.85107313402817</v>
+        <v>19.85210282884073</v>
       </c>
       <c r="S16" t="n">
-        <v>21.15267711777287</v>
+        <v>19.21759717115924</v>
       </c>
       <c r="T16" t="n">
-        <v>60.16514400244472</v>
+        <v>59.41994166930647</v>
       </c>
       <c r="U16" t="n">
-        <v>129.9156199972058</v>
+        <v>129.0195630847407</v>
       </c>
       <c r="V16" t="n">
-        <v>140.6846999999126</v>
+        <v>140.6042499996509</v>
       </c>
       <c r="W16" t="n">
-        <v>41.12191120288647</v>
+        <v>41.77576441921153</v>
       </c>
       <c r="X16" t="n">
-        <v>157.433549999302</v>
+        <v>156.9175999996507</v>
       </c>
       <c r="Y16" t="n">
-        <v>43.00375025180104</v>
+        <v>39.06969999999997</v>
       </c>
       <c r="Z16" t="n">
-        <v>572.3246754535526</v>
+        <v>566.8068191725604</v>
       </c>
     </row>
     <row r="17">
@@ -1822,34 +1822,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30.46397201363193</v>
+        <v>30.44165185853779</v>
       </c>
       <c r="D17" t="n">
-        <v>29.70076798897577</v>
+        <v>29.6790070134985</v>
       </c>
       <c r="E17" t="n">
-        <v>40.29334953379121</v>
+        <v>40.00237383526483</v>
       </c>
       <c r="F17" t="n">
-        <v>37.60398121623324</v>
+        <v>37.33242660912393</v>
       </c>
       <c r="G17" t="n">
-        <v>52.01455724699505</v>
+        <v>51.6389376397</v>
       </c>
       <c r="H17" t="n">
-        <v>47.31656987624195</v>
+        <v>47.29131175313328</v>
       </c>
       <c r="I17" t="n">
-        <v>45.2538618134648</v>
+        <v>45.22970478737824</v>
       </c>
       <c r="J17" t="n">
-        <v>48.11596831020002</v>
+        <v>48.09028345911613</v>
       </c>
       <c r="K17" t="n">
-        <v>20.65452240010321</v>
+        <v>20.82422137487527</v>
       </c>
       <c r="L17" t="n">
-        <v>20.58491596073479</v>
+        <v>20.75404304421983</v>
       </c>
       <c r="M17" t="n">
         <v>34.5</v>
@@ -1858,40 +1858,40 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>46.88841639423315</v>
+        <v>46.60242792608057</v>
       </c>
       <c r="P17" t="n">
-        <v>26.03848360502229</v>
+        <v>25.72387207354675</v>
       </c>
       <c r="Q17" t="n">
         <v>50</v>
       </c>
       <c r="R17" t="n">
-        <v>21.93549851657066</v>
+        <v>19.73883700523774</v>
       </c>
       <c r="S17" t="n">
-        <v>21.33532168485154</v>
+        <v>19.19876299476224</v>
       </c>
       <c r="T17" t="n">
-        <v>60.1647400026077</v>
+        <v>60.12065887203629</v>
       </c>
       <c r="U17" t="n">
-        <v>129.9118879970195</v>
+        <v>128.9737380840888</v>
       </c>
       <c r="V17" t="n">
-        <v>140.6863999999068</v>
+        <v>140.6112999996276</v>
       </c>
       <c r="W17" t="n">
-        <v>41.239438360838</v>
+        <v>41.57826441909511</v>
       </c>
       <c r="X17" t="n">
-        <v>157.4268999992555</v>
+        <v>156.8262999996273</v>
       </c>
       <c r="Y17" t="n">
-        <v>43.2708202014222</v>
+        <v>38.93759999999997</v>
       </c>
       <c r="Z17" t="n">
-        <v>572.7001865610497</v>
+        <v>567.047861374475</v>
       </c>
     </row>
     <row r="18">
@@ -1904,34 +1904,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30.47543425958383</v>
+        <v>30.35367636207907</v>
       </c>
       <c r="D18" t="n">
-        <v>29.68890174318685</v>
+        <v>29.57028626343076</v>
       </c>
       <c r="E18" t="n">
-        <v>40.30065390316903</v>
+        <v>39.97824023730008</v>
       </c>
       <c r="F18" t="n">
-        <v>37.59984426840428</v>
+        <v>37.29903764487392</v>
       </c>
       <c r="G18" t="n">
-        <v>52.00765782525993</v>
+        <v>51.59158567782063</v>
       </c>
       <c r="H18" t="n">
-        <v>47.31829425216841</v>
+        <v>47.27130829016405</v>
       </c>
       <c r="I18" t="n">
-        <v>45.25484464744194</v>
+        <v>45.20990764274379</v>
       </c>
       <c r="J18" t="n">
-        <v>48.1149611002906</v>
+        <v>48.06718406669654</v>
       </c>
       <c r="K18" t="n">
-        <v>20.36548892906817</v>
+        <v>20.7755538016485</v>
       </c>
       <c r="L18" t="n">
-        <v>20.30555257915529</v>
+        <v>20.71441061639886</v>
       </c>
       <c r="M18" t="n">
         <v>34.5</v>
@@ -1940,40 +1940,40 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>43.3979719535024</v>
+        <v>43.12917470152591</v>
       </c>
       <c r="P18" t="n">
-        <v>29.52227804570654</v>
+        <v>29.20762529807809</v>
       </c>
       <c r="Q18" t="n">
         <v>50</v>
       </c>
       <c r="R18" t="n">
-        <v>22.04629337004458</v>
+        <v>19.67197142666401</v>
       </c>
       <c r="S18" t="n">
-        <v>21.44286279107455</v>
+        <v>19.13352857333597</v>
       </c>
       <c r="T18" t="n">
-        <v>60.16433600277068</v>
+        <v>59.92396262550983</v>
       </c>
       <c r="U18" t="n">
-        <v>129.9081559968332</v>
+        <v>128.8688635599946</v>
       </c>
       <c r="V18" t="n">
-        <v>140.6880999999009</v>
+        <v>140.5483999996044</v>
       </c>
       <c r="W18" t="n">
-        <v>40.67104150822347</v>
+        <v>41.48996441804736</v>
       </c>
       <c r="X18" t="n">
-        <v>157.4202499992089</v>
+        <v>156.836799999604</v>
       </c>
       <c r="Y18" t="n">
-        <v>43.48915616111913</v>
+        <v>38.80549999999998</v>
       </c>
       <c r="Z18" t="n">
-        <v>572.3410396680564</v>
+        <v>566.4734906027602</v>
       </c>
     </row>
     <row r="19">
@@ -1986,34 +1986,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30.48223296433131</v>
+        <v>30.24269292236276</v>
       </c>
       <c r="D19" t="n">
-        <v>29.68169903860235</v>
+        <v>29.4484498720559</v>
       </c>
       <c r="E19" t="n">
-        <v>40.32367564014688</v>
+        <v>39.98757661332895</v>
       </c>
       <c r="F19" t="n">
-        <v>37.59962187725365</v>
+        <v>37.28622791896365</v>
       </c>
       <c r="G19" t="n">
-        <v>51.98112647924646</v>
+        <v>51.54786225555597</v>
       </c>
       <c r="H19" t="n">
-        <v>47.31348500099443</v>
+        <v>47.27187301920936</v>
       </c>
       <c r="I19" t="n">
-        <v>45.25635904484572</v>
+        <v>45.21655629541407</v>
       </c>
       <c r="J19" t="n">
-        <v>48.11995595405497</v>
+        <v>48.07763468495767</v>
       </c>
       <c r="K19" t="n">
-        <v>19.7528221456036</v>
+        <v>20.93448848847965</v>
       </c>
       <c r="L19" t="n">
-        <v>19.6884599068355</v>
+        <v>20.8662759294513</v>
       </c>
       <c r="M19" t="n">
         <v>34.5</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>42.17672288437311</v>
+        <v>41.92643773443277</v>
       </c>
       <c r="P19" t="n">
-        <v>30.73687711478927</v>
+        <v>30.44366226514796</v>
       </c>
       <c r="Q19" t="n">
         <v>50</v>
       </c>
       <c r="R19" t="n">
-        <v>22.20187312148428</v>
+        <v>19.62884905015595</v>
       </c>
       <c r="S19" t="n">
-        <v>21.54098300739241</v>
+        <v>19.04455094984403</v>
       </c>
       <c r="T19" t="n">
-        <v>60.16393200293366</v>
+        <v>59.69114279441867</v>
       </c>
       <c r="U19" t="n">
-        <v>129.904423996647</v>
+        <v>128.8216667878486</v>
       </c>
       <c r="V19" t="n">
-        <v>140.6897999998951</v>
+        <v>140.5660639995811</v>
       </c>
       <c r="W19" t="n">
-        <v>39.4412820524391</v>
+        <v>41.80076441793095</v>
       </c>
       <c r="X19" t="n">
-        <v>157.4135999991624</v>
+        <v>156.8700999995807</v>
       </c>
       <c r="Y19" t="n">
-        <v>43.74285612887668</v>
+        <v>38.67339999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>571.3558941799539</v>
+        <v>566.4231379993601</v>
       </c>
     </row>
     <row r="20">
@@ -2068,34 +2068,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.46387105196751</v>
+        <v>30.05344771004993</v>
       </c>
       <c r="D20" t="n">
-        <v>29.69965695112914</v>
+        <v>29.29952945456461</v>
       </c>
       <c r="E20" t="n">
-        <v>40.24251211051162</v>
+        <v>39.88373910425262</v>
       </c>
       <c r="F20" t="n">
-        <v>37.74322244182927</v>
+        <v>37.4067312867997</v>
       </c>
       <c r="G20" t="n">
-        <v>51.91495744411981</v>
+        <v>51.45212139400231</v>
       </c>
       <c r="H20" t="n">
-        <v>47.31139230601016</v>
+        <v>47.2968193821828</v>
       </c>
       <c r="I20" t="n">
-        <v>45.25785236000796</v>
+        <v>45.24391197053968</v>
       </c>
       <c r="J20" t="n">
-        <v>48.12225533387117</v>
+        <v>48.10743264683535</v>
       </c>
       <c r="K20" t="n">
-        <v>19.34703451562974</v>
+        <v>20.82320484835811</v>
       </c>
       <c r="L20" t="n">
-        <v>19.28372010007406</v>
+        <v>20.75505957038775</v>
       </c>
       <c r="M20" t="n">
         <v>34.5</v>
@@ -2104,40 +2104,40 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>42.70756511938761</v>
+        <v>42.49759361504995</v>
       </c>
       <c r="P20" t="n">
-        <v>30.19938487972824</v>
+        <v>29.95590638450751</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
       </c>
       <c r="R20" t="n">
-        <v>22.26585347784064</v>
+        <v>19.5712356272273</v>
       </c>
       <c r="S20" t="n">
-        <v>21.58191142524209</v>
+        <v>18.9700643727727</v>
       </c>
       <c r="T20" t="n">
-        <v>60.16352800309664</v>
+        <v>59.35297716461454</v>
       </c>
       <c r="U20" t="n">
-        <v>129.9006919964607</v>
+        <v>128.7425917850546</v>
       </c>
       <c r="V20" t="n">
-        <v>140.6914999998893</v>
+        <v>140.6481639995578</v>
       </c>
       <c r="W20" t="n">
-        <v>38.63075461570379</v>
+        <v>41.57826441874586</v>
       </c>
       <c r="X20" t="n">
-        <v>157.4069499991159</v>
+        <v>156.9534999995575</v>
       </c>
       <c r="Y20" t="n">
-        <v>43.84776490308273</v>
+        <v>38.54129999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>570.6411895173491</v>
+        <v>565.8167973675303</v>
       </c>
     </row>
     <row r="21">
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.46475917661167</v>
+        <v>30.61309580542267</v>
       </c>
       <c r="D21" t="n">
-        <v>29.69836482664796</v>
+        <v>29.84296978787694</v>
       </c>
       <c r="E21" t="n">
-        <v>40.1522172813444</v>
+        <v>39.77463096054424</v>
       </c>
       <c r="F21" t="n">
-        <v>37.92511529449473</v>
+        <v>37.56847235620739</v>
       </c>
       <c r="G21" t="n">
-        <v>51.81962742043529</v>
+        <v>51.33232226550907</v>
       </c>
       <c r="H21" t="n">
-        <v>47.30985844442188</v>
+        <v>47.2864424632718</v>
       </c>
       <c r="I21" t="n">
-        <v>45.25873019752921</v>
+        <v>45.23632942086176</v>
       </c>
       <c r="J21" t="n">
-        <v>48.12461135793238</v>
+        <v>48.10079211540101</v>
       </c>
       <c r="K21" t="n">
-        <v>20.05100173417398</v>
+        <v>20.94181553608731</v>
       </c>
       <c r="L21" t="n">
-        <v>19.98123465050923</v>
+        <v>20.86894888254213</v>
       </c>
       <c r="M21" t="n">
         <v>34.5</v>
@@ -2186,40 +2186,40 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>43.14924335055949</v>
+        <v>43.0150731674475</v>
       </c>
       <c r="P21" t="n">
-        <v>29.75105664850983</v>
+        <v>29.57737683208672</v>
       </c>
       <c r="Q21" t="n">
         <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>22.46123375195705</v>
+        <v>19.50974464904806</v>
       </c>
       <c r="S21" t="n">
-        <v>21.75861817049051</v>
+        <v>18.89945535095194</v>
       </c>
       <c r="T21" t="n">
-        <v>60.16312400325963</v>
+        <v>60.45606559329961</v>
       </c>
       <c r="U21" t="n">
-        <v>129.8969599962744</v>
+        <v>128.6754255822607</v>
       </c>
       <c r="V21" t="n">
-        <v>140.6931999998835</v>
+        <v>140.6235639995346</v>
       </c>
       <c r="W21" t="n">
-        <v>40.0322363846832</v>
+        <v>41.81076441862945</v>
       </c>
       <c r="X21" t="n">
-        <v>157.4002999990693</v>
+        <v>157.0924499995342</v>
       </c>
       <c r="Y21" t="n">
-        <v>44.21985192244756</v>
+        <v>38.4092</v>
       </c>
       <c r="Z21" t="n">
-        <v>572.4056723056176</v>
+        <v>567.0674695932585</v>
       </c>
     </row>
     <row r="22">
@@ -2232,34 +2232,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.48368260298833</v>
+        <v>30.58114421696714</v>
       </c>
       <c r="D22" t="n">
-        <v>29.67903740043428</v>
+        <v>29.7739264243116</v>
       </c>
       <c r="E22" t="n">
-        <v>40.10601349406064</v>
+        <v>39.70789498783981</v>
       </c>
       <c r="F22" t="n">
-        <v>38.02023743747521</v>
+        <v>37.6428237078107</v>
       </c>
       <c r="G22" t="n">
-        <v>51.76697706455231</v>
+        <v>51.25310421145613</v>
       </c>
       <c r="H22" t="n">
-        <v>47.30623748322652</v>
+        <v>47.29902999721229</v>
       </c>
       <c r="I22" t="n">
-        <v>45.26003593656272</v>
+        <v>45.25314020582252</v>
       </c>
       <c r="J22" t="n">
-        <v>48.12862658008839</v>
+        <v>48.12129379647644</v>
       </c>
       <c r="K22" t="n">
-        <v>19.55842984645684</v>
+        <v>21.1208612335728</v>
       </c>
       <c r="L22" t="n">
-        <v>19.48114566892019</v>
+        <v>21.03740318494023</v>
       </c>
       <c r="M22" t="n">
         <v>34.5</v>
@@ -2268,40 +2268,40 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>43.5208058535347</v>
+        <v>43.38486369598934</v>
       </c>
       <c r="P22" t="n">
-        <v>29.37284414548806</v>
+        <v>29.21233630352156</v>
       </c>
       <c r="Q22" t="n">
         <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>22.29234239238749</v>
+        <v>19.45016635539692</v>
       </c>
       <c r="S22" t="n">
-        <v>21.57803914555193</v>
+        <v>18.82693364460309</v>
       </c>
       <c r="T22" t="n">
-        <v>60.16272000342261</v>
+        <v>60.35507064127874</v>
       </c>
       <c r="U22" t="n">
-        <v>129.8932279960882</v>
+        <v>128.6038229071066</v>
       </c>
       <c r="V22" t="n">
-        <v>140.6948999998776</v>
+        <v>140.6734639995113</v>
       </c>
       <c r="W22" t="n">
-        <v>39.03957551537702</v>
+        <v>42.15826441851303</v>
       </c>
       <c r="X22" t="n">
-        <v>157.3936499990228</v>
+        <v>157.0971999995109</v>
       </c>
       <c r="Y22" t="n">
-        <v>43.87038153793942</v>
+        <v>38.2771</v>
       </c>
       <c r="Z22" t="n">
-        <v>571.0544550517277</v>
+        <v>567.1649219659205</v>
       </c>
     </row>
     <row r="23">
@@ -2314,34 +2314,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30.48089004341457</v>
+        <v>30.44234993357032</v>
       </c>
       <c r="D23" t="n">
-        <v>29.68142596017101</v>
+        <v>29.64389669461447</v>
       </c>
       <c r="E23" t="n">
-        <v>40.08077118455392</v>
+        <v>39.66552942297597</v>
       </c>
       <c r="F23" t="n">
-        <v>38.06928273478275</v>
+        <v>37.6748802430739</v>
       </c>
       <c r="G23" t="n">
-        <v>51.7394420765652</v>
+        <v>51.2034150382628</v>
       </c>
       <c r="H23" t="n">
-        <v>47.30174512411944</v>
+        <v>47.26051529459119</v>
       </c>
       <c r="I23" t="n">
-        <v>45.26127978409305</v>
+        <v>45.22182849440318</v>
       </c>
       <c r="J23" t="n">
-        <v>48.13357509165932</v>
+        <v>48.09162021049359</v>
       </c>
       <c r="K23" t="n">
-        <v>21.15029000988152</v>
+        <v>20.79274175990592</v>
       </c>
       <c r="L23" t="n">
-        <v>21.17346264470365</v>
+        <v>20.81552265849068</v>
       </c>
       <c r="M23" t="n">
         <v>34.5</v>
@@ -2350,40 +2350,40 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>43.82639847140388</v>
+        <v>43.68115812855589</v>
       </c>
       <c r="P23" t="n">
-        <v>29.06060152757238</v>
+        <v>28.90604187093176</v>
       </c>
       <c r="Q23" t="n">
         <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>22.28010504892044</v>
+        <v>19.32589743414679</v>
       </c>
       <c r="S23" t="n">
-        <v>21.69584018141247</v>
+        <v>18.81910256585322</v>
       </c>
       <c r="T23" t="n">
-        <v>60.16231600358559</v>
+        <v>60.0862466281848</v>
       </c>
       <c r="U23" t="n">
-        <v>129.8894959959019</v>
+        <v>128.5438247043127</v>
       </c>
       <c r="V23" t="n">
-        <v>140.6965999998718</v>
+        <v>140.573963999488</v>
       </c>
       <c r="W23" t="n">
-        <v>42.32375265458517</v>
+        <v>41.6082644183966</v>
       </c>
       <c r="X23" t="n">
-        <v>157.3869999989763</v>
+        <v>157.0871999994877</v>
       </c>
       <c r="Y23" t="n">
-        <v>43.97594523033291</v>
+        <v>38.14500000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>574.4351098832535</v>
+        <v>566.0444997498697</v>
       </c>
     </row>
     <row r="24">
@@ -2396,34 +2396,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>30.48672951884636</v>
+        <v>30.55438145396888</v>
       </c>
       <c r="D24" t="n">
-        <v>29.67518248490222</v>
+        <v>29.74103354704965</v>
       </c>
       <c r="E24" t="n">
-        <v>40.06833497501962</v>
+        <v>39.63721095736006</v>
       </c>
       <c r="F24" t="n">
-        <v>38.08858362154491</v>
+        <v>37.67876117176954</v>
       </c>
       <c r="G24" t="n">
-        <v>51.72884539915106</v>
+        <v>51.17225756810504</v>
       </c>
       <c r="H24" t="n">
-        <v>47.30075690143077</v>
+        <v>47.27169835386824</v>
       </c>
       <c r="I24" t="n">
-        <v>45.26214410916155</v>
+        <v>45.2343379543865</v>
       </c>
       <c r="J24" t="n">
-        <v>48.13539898927364</v>
+        <v>48.10582769120992</v>
       </c>
       <c r="K24" t="n">
-        <v>21.27002038191731</v>
+        <v>21.12141386071595</v>
       </c>
       <c r="L24" t="n">
-        <v>21.34347041443031</v>
+        <v>21.19435072240833</v>
       </c>
       <c r="M24" t="n">
         <v>34.5</v>
@@ -2432,40 +2432,40 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>44.07802397442703</v>
+        <v>43.96882385574464</v>
       </c>
       <c r="P24" t="n">
-        <v>28.80232602450269</v>
+        <v>28.68152614371972</v>
       </c>
       <c r="Q24" t="n">
         <v>50</v>
       </c>
       <c r="R24" t="n">
-        <v>22.3401940824494</v>
+        <v>19.23614164890231</v>
       </c>
       <c r="S24" t="n">
-        <v>21.80668210179831</v>
+        <v>18.7767583510977</v>
       </c>
       <c r="T24" t="n">
-        <v>60.16191200374857</v>
+        <v>60.29541500101853</v>
       </c>
       <c r="U24" t="n">
-        <v>129.8857639957156</v>
+        <v>128.4882296972347</v>
       </c>
       <c r="V24" t="n">
-        <v>140.698299999866</v>
+        <v>140.6118639994647</v>
       </c>
       <c r="W24" t="n">
-        <v>42.61349079634761</v>
+        <v>42.31576458312428</v>
       </c>
       <c r="X24" t="n">
-        <v>157.3803499989297</v>
+        <v>157.1503499994644</v>
       </c>
       <c r="Y24" t="n">
-        <v>44.14687618424771</v>
+        <v>38.01290000000002</v>
       </c>
       <c r="Z24" t="n">
-        <v>574.8866929788552</v>
+        <v>566.8745232803066</v>
       </c>
     </row>
     <row r="25">
@@ -2478,34 +2478,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30.4796829484202</v>
+        <v>30.59156418901063</v>
       </c>
       <c r="D25" t="n">
-        <v>29.68182505549134</v>
+        <v>29.79077761302995</v>
       </c>
       <c r="E25" t="n">
-        <v>40.05557435618559</v>
+        <v>39.60336721885398</v>
       </c>
       <c r="F25" t="n">
-        <v>38.09435179130082</v>
+        <v>37.66428586292681</v>
       </c>
       <c r="G25" t="n">
-        <v>51.7321058480429</v>
+        <v>51.1480765869554</v>
       </c>
       <c r="H25" t="n">
-        <v>47.30077246801599</v>
+        <v>47.27225215278565</v>
       </c>
       <c r="I25" t="n">
-        <v>45.26490488106381</v>
+        <v>45.23761210573012</v>
       </c>
       <c r="J25" t="n">
-        <v>48.13432265078038</v>
+        <v>48.10529974092563</v>
       </c>
       <c r="K25" t="n">
-        <v>21.25504567533599</v>
+        <v>21.07537115377398</v>
       </c>
       <c r="L25" t="n">
-        <v>21.3542080635208</v>
+        <v>21.17369529606998</v>
       </c>
       <c r="M25" t="n">
         <v>34.5</v>
@@ -2514,40 +2514,40 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>44.30862983912458</v>
+        <v>44.1313578164751</v>
       </c>
       <c r="P25" t="n">
-        <v>28.5650701597586</v>
+        <v>28.40899218296603</v>
       </c>
       <c r="Q25" t="n">
         <v>50</v>
       </c>
       <c r="R25" t="n">
-        <v>22.35243701165845</v>
+        <v>19.29842646641204</v>
       </c>
       <c r="S25" t="n">
-        <v>21.85664393571735</v>
+        <v>18.87037353358798</v>
       </c>
       <c r="T25" t="n">
-        <v>60.16150800391155</v>
+        <v>60.38234180204059</v>
       </c>
       <c r="U25" t="n">
-        <v>129.8820319955293</v>
+        <v>128.4157296687362</v>
       </c>
       <c r="V25" t="n">
-        <v>140.6999999998602</v>
+        <v>140.6151639994414</v>
       </c>
       <c r="W25" t="n">
-        <v>42.60925373885679</v>
+        <v>42.24906644984396</v>
       </c>
       <c r="X25" t="n">
-        <v>157.3736999988832</v>
+        <v>157.0403499994411</v>
       </c>
       <c r="Y25" t="n">
-        <v>44.20908094737581</v>
+        <v>38.16880000000002</v>
       </c>
       <c r="Z25" t="n">
-        <v>574.9355746844168</v>
+        <v>566.8714519195033</v>
       </c>
     </row>
   </sheetData>
